--- a/Docs/Requisitos.xlsx
+++ b/Docs/Requisitos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a0706bd09e6b5aa/Trabalho/DEV/GestaoPiscina/Docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E92D66D-165D-42BC-BCAC-25A90C099D40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{9E92D66D-165D-42BC-BCAC-25A90C099D40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAD9F22D-9A6A-4DF6-992B-A61449716292}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{0FF7F3A3-45CB-4B48-859E-5FE7B9E0D8E5}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="12" r:id="rId2"/>
+    <pivotCache cacheId="43" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -47,9 +47,6 @@
     <t>Tester</t>
   </si>
   <si>
-    <t>Cadastros básicos: Clientes, Piscinas, Produtos e Usuários</t>
-  </si>
-  <si>
     <t>Gestão de Ordens de Serviço (OS) com checklist obrigatório</t>
   </si>
   <si>
@@ -159,6 +156,9 @@
   </si>
   <si>
     <t>Valor</t>
+  </si>
+  <si>
+    <t>Cadastros básicos: Clientes, Piscinas, Produtos, Síndicos e Usuários</t>
   </si>
 </sst>
 </file>
@@ -166,7 +166,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -208,7 +208,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -216,7 +216,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -226,29 +225,47 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="15">
     <dxf>
-      <numFmt numFmtId="169" formatCode="&quot;R$&quot;\ #,##0.00"/>
+      <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -257,29 +274,12 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="169" formatCode="&quot;R$&quot;\ #,##0.00"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="169" formatCode="&quot;R$&quot;\ #,##0.00"/>
       <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -299,23 +299,19 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Daivisson Sobral" refreshedDate="45864.129584490744" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="21" xr:uid="{9D95A224-3EBA-4889-870B-02133977CB25}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Daivisson Sobral" refreshedDate="45869.700718981483" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="21" xr:uid="{9D95A224-3EBA-4889-870B-02133977CB25}">
   <cacheSource type="worksheet">
     <worksheetSource name="Tabela1"/>
   </cacheSource>
   <cacheFields count="6">
     <cacheField name="Fase" numFmtId="0">
-      <sharedItems count="3">
-        <s v="Fase 1"/>
-        <s v="Fase 2"/>
-        <s v="Fase 3"/>
-      </sharedItems>
+      <sharedItems/>
     </cacheField>
     <cacheField name="Item" numFmtId="0">
-      <sharedItems count="21">
+      <sharedItems count="22">
         <s v="Documentação"/>
         <s v="Configuração do ambiente e arquitetura"/>
-        <s v="Cadastros básicos: Clientes, Piscinas, Produtos e Usuários"/>
+        <s v="Cadastros básicos: Clientes, Piscinas, Produtos, Síndicos e Usuários"/>
         <s v="Gestão de Ordens de Serviço (OS) com checklist obrigatório"/>
         <s v="Upload de fotos e vídeos no fluxo da OS"/>
         <s v="Emissão de relatório diário básico em PDF enviado automaticamente ao cliente"/>
@@ -334,10 +330,11 @@
         <s v="Operação offline (PWA) com sincronização automática"/>
         <s v="Melhorias de usabilidade (UI/UX) e performance"/>
         <s v="Encerramento"/>
+        <s v="Cadastros básicos: Clientes, Piscinas, Produtos e Usuários" u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Horas" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="4" maxValue="32"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="4" maxValue="40"/>
     </cacheField>
     <cacheField name="Recurso" numFmtId="0">
       <sharedItems count="4">
@@ -347,11 +344,11 @@
         <s v="Consultor"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="Valor Unit." numFmtId="169">
+    <cacheField name="Valor Unit." numFmtId="164">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="75" maxValue="120"/>
     </cacheField>
-    <cacheField name="Valor Total" numFmtId="169">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="300" maxValue="3200"/>
+    <cacheField name="Valor Total" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="300" maxValue="4000"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -365,7 +362,7 @@
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="21">
   <r>
-    <x v="0"/>
+    <s v="Fase 1"/>
     <x v="0"/>
     <n v="8"/>
     <x v="0"/>
@@ -373,7 +370,7 @@
     <n v="960"/>
   </r>
   <r>
-    <x v="0"/>
+    <s v="Fase 1"/>
     <x v="1"/>
     <n v="20"/>
     <x v="0"/>
@@ -381,15 +378,15 @@
     <n v="2400"/>
   </r>
   <r>
-    <x v="0"/>
+    <s v="Fase 1"/>
     <x v="2"/>
-    <n v="30"/>
+    <n v="40"/>
     <x v="1"/>
     <n v="100"/>
-    <n v="3000"/>
-  </r>
-  <r>
-    <x v="0"/>
+    <n v="4000"/>
+  </r>
+  <r>
+    <s v="Fase 1"/>
     <x v="3"/>
     <n v="30"/>
     <x v="1"/>
@@ -397,7 +394,7 @@
     <n v="3000"/>
   </r>
   <r>
-    <x v="0"/>
+    <s v="Fase 1"/>
     <x v="4"/>
     <n v="20"/>
     <x v="1"/>
@@ -405,7 +402,7 @@
     <n v="2000"/>
   </r>
   <r>
-    <x v="0"/>
+    <s v="Fase 1"/>
     <x v="5"/>
     <n v="20"/>
     <x v="1"/>
@@ -413,7 +410,7 @@
     <n v="2000"/>
   </r>
   <r>
-    <x v="0"/>
+    <s v="Fase 1"/>
     <x v="6"/>
     <n v="8"/>
     <x v="1"/>
@@ -421,7 +418,7 @@
     <n v="800"/>
   </r>
   <r>
-    <x v="0"/>
+    <s v="Fase 1"/>
     <x v="7"/>
     <n v="16"/>
     <x v="1"/>
@@ -429,7 +426,7 @@
     <n v="1600"/>
   </r>
   <r>
-    <x v="0"/>
+    <s v="Fase 1"/>
     <x v="8"/>
     <n v="24"/>
     <x v="2"/>
@@ -437,7 +434,7 @@
     <n v="1800"/>
   </r>
   <r>
-    <x v="0"/>
+    <s v="Fase 1"/>
     <x v="9"/>
     <n v="16"/>
     <x v="3"/>
@@ -445,7 +442,7 @@
     <n v="1200"/>
   </r>
   <r>
-    <x v="0"/>
+    <s v="Fase 1"/>
     <x v="10"/>
     <n v="4"/>
     <x v="3"/>
@@ -453,7 +450,7 @@
     <n v="300"/>
   </r>
   <r>
-    <x v="0"/>
+    <s v="Fase 1"/>
     <x v="11"/>
     <n v="16"/>
     <x v="3"/>
@@ -461,7 +458,7 @@
     <n v="1200"/>
   </r>
   <r>
-    <x v="1"/>
+    <s v="Fase 2"/>
     <x v="12"/>
     <n v="20"/>
     <x v="1"/>
@@ -469,7 +466,7 @@
     <n v="2000"/>
   </r>
   <r>
-    <x v="1"/>
+    <s v="Fase 2"/>
     <x v="13"/>
     <n v="20"/>
     <x v="1"/>
@@ -477,7 +474,7 @@
     <n v="2000"/>
   </r>
   <r>
-    <x v="1"/>
+    <s v="Fase 2"/>
     <x v="14"/>
     <n v="24"/>
     <x v="1"/>
@@ -485,7 +482,7 @@
     <n v="2400"/>
   </r>
   <r>
-    <x v="1"/>
+    <s v="Fase 2"/>
     <x v="15"/>
     <n v="20"/>
     <x v="1"/>
@@ -493,7 +490,7 @@
     <n v="2000"/>
   </r>
   <r>
-    <x v="2"/>
+    <s v="Fase 3"/>
     <x v="16"/>
     <n v="16"/>
     <x v="1"/>
@@ -501,7 +498,7 @@
     <n v="1600"/>
   </r>
   <r>
-    <x v="2"/>
+    <s v="Fase 3"/>
     <x v="17"/>
     <n v="20"/>
     <x v="1"/>
@@ -509,7 +506,7 @@
     <n v="2000"/>
   </r>
   <r>
-    <x v="2"/>
+    <s v="Fase 3"/>
     <x v="18"/>
     <n v="32"/>
     <x v="1"/>
@@ -517,7 +514,7 @@
     <n v="3200"/>
   </r>
   <r>
-    <x v="2"/>
+    <s v="Fase 3"/>
     <x v="19"/>
     <n v="20"/>
     <x v="1"/>
@@ -525,7 +522,7 @@
     <n v="2000"/>
   </r>
   <r>
-    <x v="2"/>
+    <s v="Fase 3"/>
     <x v="20"/>
     <n v="4"/>
     <x v="0"/>
@@ -536,22 +533,15 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B852A398-2C91-44C4-B090-B55E20C8CCE9}" name="Tabela dinâmica2" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Recurso &gt; Item">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B852A398-2C91-44C4-B090-B55E20C8CCE9}" name="Tabela dinâmica2" cacheId="43" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Recurso &gt; Item">
   <location ref="T2:V28" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
-      <items count="22">
+      <items count="23">
         <item x="6"/>
         <item x="15"/>
-        <item x="2"/>
+        <item m="1" x="21"/>
         <item x="1"/>
         <item x="13"/>
         <item x="0"/>
@@ -570,6 +560,7 @@
         <item x="9"/>
         <item x="8"/>
         <item x="4"/>
+        <item x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -583,8 +574,8 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField numFmtId="169" showAll="0"/>
-    <pivotField dataField="1" numFmtId="169" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
   </pivotFields>
   <rowFields count="2">
     <field x="3"/>
@@ -625,9 +616,6 @@
       <x v="1"/>
     </i>
     <i r="1">
-      <x v="2"/>
-    </i>
-    <i r="1">
       <x v="4"/>
     </i>
     <i r="1">
@@ -659,6 +647,9 @@
     </i>
     <i r="1">
       <x v="20"/>
+    </i>
+    <i r="1">
+      <x v="21"/>
     </i>
     <i>
       <x v="3"/>
@@ -683,7 +674,7 @@
   </colItems>
   <dataFields count="2">
     <dataField name="Soma de Horas" fld="2" baseField="0" baseItem="0"/>
-    <dataField name="Soma de Valor Total" fld="5" baseField="0" baseItem="0" numFmtId="169"/>
+    <dataField name="Soma de Valor Total" fld="5" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -698,17 +689,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C67377A9-8B67-4460-B9FA-2F431678656F}" name="Tabela1" displayName="Tabela1" ref="H2:M24" totalsRowCount="1" headerRowDxfId="11" dataDxfId="9" totalsRowDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C67377A9-8B67-4460-B9FA-2F431678656F}" name="Tabela1" displayName="Tabela1" ref="H2:M24" totalsRowCount="1" headerRowDxfId="14" dataDxfId="13" totalsRowDxfId="12">
   <autoFilter ref="H2:M23" xr:uid="{C67377A9-8B67-4460-B9FA-2F431678656F}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{9A00E71B-0C22-4676-B207-02FEAD7B1D46}" name="Fase" totalsRowLabel="Total" dataDxfId="8" totalsRowDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{5FB9431E-42B7-4383-821B-59A8167AFBFC}" name="Item" dataDxfId="6" totalsRowDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{C2B35993-B025-42F7-831A-366A5C1002A2}" name="Horas" totalsRowFunction="sum" dataDxfId="7" totalsRowDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{9C63D28F-2D75-4750-9E8C-F8C8EFA23D8F}" name="Recurso" dataDxfId="14" totalsRowDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{92E94915-15DE-4828-86C2-9DF73A0005EF}" name="Valor Unit." dataDxfId="13" totalsRowDxfId="1">
+    <tableColumn id="1" xr3:uid="{9A00E71B-0C22-4676-B207-02FEAD7B1D46}" name="Fase" totalsRowLabel="Total" dataDxfId="11" totalsRowDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{5FB9431E-42B7-4383-821B-59A8167AFBFC}" name="Item" dataDxfId="9" totalsRowDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{C2B35993-B025-42F7-831A-366A5C1002A2}" name="Horas" totalsRowFunction="sum" dataDxfId="7" totalsRowDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{9C63D28F-2D75-4750-9E8C-F8C8EFA23D8F}" name="Recurso" dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{92E94915-15DE-4828-86C2-9DF73A0005EF}" name="Valor Unit." dataDxfId="3" totalsRowDxfId="2">
       <calculatedColumnFormula>VLOOKUP(Tabela1[[#This Row],[Recurso]],Tabela2[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{E7D5748C-E54E-48F9-A92A-197C4B2B2159}" name="Valor Total" totalsRowFunction="sum" dataDxfId="12" totalsRowDxfId="0">
+    <tableColumn id="6" xr3:uid="{E7D5748C-E54E-48F9-A92A-197C4B2B2159}" name="Valor Total" totalsRowFunction="sum" dataDxfId="1" totalsRowDxfId="0">
       <calculatedColumnFormula>L3*J3</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1044,12 +1035,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48E4F75F-1DD9-4A91-8E30-81F4CE3B2615}">
-  <dimension ref="B2:V28"/>
+  <dimension ref="B2:V31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="46.109375" style="7" customWidth="1"/>
+    <col min="9" max="9" width="46.109375" style="6" customWidth="1"/>
     <col min="10" max="10" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.5546875" customWidth="1"/>
     <col min="12" max="12" width="12.21875" bestFit="1" customWidth="1"/>
@@ -1065,67 +1056,67 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="I2" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="L2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="T2" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="U2" t="s">
+        <v>34</v>
+      </c>
+      <c r="V2" t="s">
         <v>35</v>
-      </c>
-      <c r="V2" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3">
         <v>120</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="J3" s="1">
         <v>8</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" s="10">
+        <v>23</v>
+      </c>
+      <c r="L3" s="9">
         <f>VLOOKUP(Tabela1[[#This Row],[Recurso]],Tabela2[],2,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="M3" s="10">
-        <f>L3*J3</f>
+      <c r="M3" s="9">
+        <f t="shared" ref="M3:M23" si="0">L3*J3</f>
         <v>960</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="U3" s="6">
+        <v>23</v>
+      </c>
+      <c r="U3" s="11">
         <v>32</v>
       </c>
       <c r="V3" s="2">
@@ -1134,35 +1125,35 @@
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4">
         <v>100</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="J4" s="1">
         <v>20</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="L4" s="10">
+        <v>23</v>
+      </c>
+      <c r="L4" s="9">
         <f>VLOOKUP(Tabela1[[#This Row],[Recurso]],Tabela2[],2,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="M4" s="10">
-        <f>L4*J4</f>
+      <c r="M4" s="9">
+        <f t="shared" si="0"/>
         <v>2400</v>
       </c>
       <c r="T4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="U4" s="6">
+        <v>21</v>
+      </c>
+      <c r="U4" s="11">
         <v>20</v>
       </c>
       <c r="V4" s="2">
@@ -1177,29 +1168,29 @@
         <v>75</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="J5" s="1">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="K5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" s="9">
+        <f>VLOOKUP(Tabela1[[#This Row],[Recurso]],Tabela2[],2,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="M5" s="9">
+        <f t="shared" si="0"/>
+        <v>4000</v>
+      </c>
+      <c r="T5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="L5" s="10">
-        <f>VLOOKUP(Tabela1[[#This Row],[Recurso]],Tabela2[],2,FALSE)</f>
-        <v>100</v>
-      </c>
-      <c r="M5" s="10">
-        <f>L5*J5</f>
-        <v>3000</v>
-      </c>
-      <c r="T5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="U5" s="6">
+      <c r="U5" s="11">
         <v>8</v>
       </c>
       <c r="V5" s="2">
@@ -1208,35 +1199,35 @@
     </row>
     <row r="6" spans="2:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C6">
         <v>75</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>3</v>
+        <v>24</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>2</v>
       </c>
       <c r="J6" s="1">
         <v>30</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L6" s="10">
+        <v>19</v>
+      </c>
+      <c r="L6" s="9">
         <f>VLOOKUP(Tabela1[[#This Row],[Recurso]],Tabela2[],2,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="M6" s="10">
-        <f>L6*J6</f>
+      <c r="M6" s="9">
+        <f t="shared" si="0"/>
         <v>3000</v>
       </c>
       <c r="T6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="U6" s="6">
+        <v>22</v>
+      </c>
+      <c r="U6" s="11">
         <v>4</v>
       </c>
       <c r="V6" s="2">
@@ -1245,29 +1236,29 @@
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.3">
       <c r="H7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>4</v>
+        <v>24</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="J7" s="1">
         <v>20</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L7" s="10">
+        <v>19</v>
+      </c>
+      <c r="L7" s="9">
         <f>VLOOKUP(Tabela1[[#This Row],[Recurso]],Tabela2[],2,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="M7" s="10">
-        <f>L7*J7</f>
+      <c r="M7" s="9">
+        <f t="shared" si="0"/>
         <v>2000</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U7" s="6">
+        <v>31</v>
+      </c>
+      <c r="U7" s="11">
         <v>36</v>
       </c>
       <c r="V7" s="2">
@@ -1276,29 +1267,29 @@
     </row>
     <row r="8" spans="2:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="H8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>5</v>
+        <v>24</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>4</v>
       </c>
       <c r="J8" s="1">
         <v>20</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L8" s="10">
+        <v>19</v>
+      </c>
+      <c r="L8" s="9">
         <f>VLOOKUP(Tabela1[[#This Row],[Recurso]],Tabela2[],2,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="M8" s="10">
-        <f>L8*J8</f>
+      <c r="M8" s="9">
+        <f t="shared" si="0"/>
         <v>2000</v>
       </c>
       <c r="T8" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="U8" s="6">
+        <v>29</v>
+      </c>
+      <c r="U8" s="11">
         <v>4</v>
       </c>
       <c r="V8" s="2">
@@ -1307,29 +1298,29 @@
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.3">
       <c r="H9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>6</v>
+        <v>24</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>5</v>
       </c>
       <c r="J9" s="1">
         <v>8</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L9" s="10">
+        <v>19</v>
+      </c>
+      <c r="L9" s="9">
         <f>VLOOKUP(Tabela1[[#This Row],[Recurso]],Tabela2[],2,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="M9" s="10">
-        <f>L9*J9</f>
+      <c r="M9" s="9">
+        <f t="shared" si="0"/>
         <v>800</v>
       </c>
       <c r="T9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="U9" s="6">
+        <v>30</v>
+      </c>
+      <c r="U9" s="11">
         <v>16</v>
       </c>
       <c r="V9" s="2">
@@ -1338,29 +1329,29 @@
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.3">
       <c r="H10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>7</v>
+        <v>24</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>6</v>
       </c>
       <c r="J10" s="1">
         <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L10" s="10">
+        <v>19</v>
+      </c>
+      <c r="L10" s="9">
         <f>VLOOKUP(Tabela1[[#This Row],[Recurso]],Tabela2[],2,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="M10" s="10">
-        <f>L10*J10</f>
+      <c r="M10" s="9">
+        <f t="shared" si="0"/>
         <v>1600</v>
       </c>
       <c r="T10" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="U10" s="6">
+        <v>28</v>
+      </c>
+      <c r="U10" s="11">
         <v>16</v>
       </c>
       <c r="V10" s="2">
@@ -1369,10 +1360,10 @@
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.3">
       <c r="H11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>28</v>
+        <v>24</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>27</v>
       </c>
       <c r="J11" s="1">
         <v>24</v>
@@ -1380,49 +1371,49 @@
       <c r="K11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="L11" s="10">
+      <c r="L11" s="9">
         <f>VLOOKUP(Tabela1[[#This Row],[Recurso]],Tabela2[],2,FALSE)</f>
         <v>75</v>
       </c>
-      <c r="M11" s="10">
-        <f>L11*J11</f>
+      <c r="M11" s="9">
+        <f t="shared" si="0"/>
         <v>1800</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="U11" s="6">
-        <v>296</v>
+        <v>19</v>
+      </c>
+      <c r="U11" s="11">
+        <v>306</v>
       </c>
       <c r="V11" s="2">
-        <v>29600</v>
+        <v>30600</v>
       </c>
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.3">
       <c r="H12" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>29</v>
+        <v>24</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>28</v>
       </c>
       <c r="J12" s="1">
         <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="L12" s="10">
+        <v>31</v>
+      </c>
+      <c r="L12" s="9">
         <f>VLOOKUP(Tabela1[[#This Row],[Recurso]],Tabela2[],2,FALSE)</f>
         <v>75</v>
       </c>
-      <c r="M12" s="10">
-        <f>L12*J12</f>
+      <c r="M12" s="9">
+        <f t="shared" si="0"/>
         <v>1200</v>
       </c>
       <c r="T12" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="U12" s="6">
+        <v>5</v>
+      </c>
+      <c r="U12" s="11">
         <v>8</v>
       </c>
       <c r="V12" s="2">
@@ -1431,29 +1422,29 @@
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.3">
       <c r="H13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>30</v>
+        <v>24</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="J13" s="1">
         <v>4</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="L13" s="10">
+        <v>31</v>
+      </c>
+      <c r="L13" s="9">
         <f>VLOOKUP(Tabela1[[#This Row],[Recurso]],Tabela2[],2,FALSE)</f>
         <v>75</v>
       </c>
-      <c r="M13" s="10">
-        <f>L13*J13</f>
+      <c r="M13" s="9">
+        <f t="shared" si="0"/>
         <v>300</v>
       </c>
       <c r="T13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="U13" s="6">
+        <v>10</v>
+      </c>
+      <c r="U13" s="11">
         <v>20</v>
       </c>
       <c r="V13" s="2">
@@ -1462,60 +1453,60 @@
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.3">
       <c r="H14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>31</v>
+        <v>24</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>30</v>
       </c>
       <c r="J14" s="1">
         <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="L14" s="10">
+        <v>31</v>
+      </c>
+      <c r="L14" s="9">
         <f>VLOOKUP(Tabela1[[#This Row],[Recurso]],Tabela2[],2,FALSE)</f>
         <v>75</v>
       </c>
-      <c r="M14" s="10">
-        <f>L14*J14</f>
+      <c r="M14" s="9">
+        <f t="shared" si="0"/>
         <v>1200</v>
       </c>
       <c r="T14" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="U14" s="6">
-        <v>30</v>
+        <v>8</v>
+      </c>
+      <c r="U14" s="11">
+        <v>20</v>
       </c>
       <c r="V14" s="2">
-        <v>3000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.3">
       <c r="H15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>8</v>
+        <v>25</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>7</v>
       </c>
       <c r="J15" s="1">
         <v>20</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L15" s="10">
+        <v>19</v>
+      </c>
+      <c r="L15" s="9">
         <f>VLOOKUP(Tabela1[[#This Row],[Recurso]],Tabela2[],2,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="M15" s="10">
-        <f>L15*J15</f>
+      <c r="M15" s="9">
+        <f t="shared" si="0"/>
         <v>2000</v>
       </c>
       <c r="T15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="U15" s="6">
+        <v>4</v>
+      </c>
+      <c r="U15" s="11">
         <v>20</v>
       </c>
       <c r="V15" s="2">
@@ -1524,29 +1515,29 @@
     </row>
     <row r="16" spans="2:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="H16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>9</v>
+        <v>25</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>8</v>
       </c>
       <c r="J16" s="1">
         <v>20</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L16" s="10">
+        <v>19</v>
+      </c>
+      <c r="L16" s="9">
         <f>VLOOKUP(Tabela1[[#This Row],[Recurso]],Tabela2[],2,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="M16" s="10">
-        <f>L16*J16</f>
+      <c r="M16" s="9">
+        <f t="shared" si="0"/>
         <v>2000</v>
       </c>
       <c r="T16" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="U16" s="6">
+        <v>12</v>
+      </c>
+      <c r="U16" s="11">
         <v>20</v>
       </c>
       <c r="V16" s="2">
@@ -1555,244 +1546,244 @@
     </row>
     <row r="17" spans="8:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="H17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>10</v>
+        <v>25</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>9</v>
       </c>
       <c r="J17" s="1">
         <v>24</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L17" s="10">
+        <v>19</v>
+      </c>
+      <c r="L17" s="9">
         <f>VLOOKUP(Tabela1[[#This Row],[Recurso]],Tabela2[],2,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="M17" s="10">
-        <f>L17*J17</f>
+      <c r="M17" s="9">
+        <f t="shared" si="0"/>
         <v>2400</v>
       </c>
       <c r="T17" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="U17" s="6">
-        <v>20</v>
+        <v>2</v>
+      </c>
+      <c r="U17" s="11">
+        <v>30</v>
       </c>
       <c r="V17" s="2">
-        <v>2000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="18" spans="8:22" x14ac:dyDescent="0.3">
       <c r="H18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>11</v>
+        <v>25</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>10</v>
       </c>
       <c r="J18" s="1">
         <v>20</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L18" s="10">
+        <v>19</v>
+      </c>
+      <c r="L18" s="9">
         <f>VLOOKUP(Tabela1[[#This Row],[Recurso]],Tabela2[],2,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="M18" s="10">
-        <f>L18*J18</f>
+      <c r="M18" s="9">
+        <f t="shared" si="0"/>
         <v>2000</v>
       </c>
       <c r="T18" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="U18" s="6">
-        <v>30</v>
+        <v>9</v>
+      </c>
+      <c r="U18" s="11">
+        <v>24</v>
       </c>
       <c r="V18" s="2">
-        <v>3000</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="19" spans="8:22" x14ac:dyDescent="0.3">
       <c r="H19" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>12</v>
+        <v>26</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="J19" s="1">
         <v>16</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L19" s="10">
+        <v>19</v>
+      </c>
+      <c r="L19" s="9">
         <f>VLOOKUP(Tabela1[[#This Row],[Recurso]],Tabela2[],2,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="M19" s="10">
-        <f>L19*J19</f>
+      <c r="M19" s="9">
+        <f t="shared" si="0"/>
         <v>1600</v>
       </c>
       <c r="P19" s="2">
-        <f>Tabela1[[#Totals],[Valor Total]]/4</f>
-        <v>9485</v>
+        <f>Tabela1[[#Totals],[Valor Total]]/5</f>
+        <v>7788</v>
       </c>
       <c r="T19" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="U19" s="6">
-        <v>24</v>
+        <v>6</v>
+      </c>
+      <c r="U19" s="11">
+        <v>16</v>
       </c>
       <c r="V19" s="2">
-        <v>2400</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="20" spans="8:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="H20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>13</v>
+        <v>26</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="J20" s="1">
         <v>20</v>
       </c>
       <c r="K20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L20" s="9">
+        <f>VLOOKUP(Tabela1[[#This Row],[Recurso]],Tabela2[],2,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="M20" s="9">
+        <f t="shared" si="0"/>
+        <v>2000</v>
+      </c>
+      <c r="T20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="U20" s="11">
         <v>20</v>
       </c>
-      <c r="L20" s="10">
-        <f>VLOOKUP(Tabela1[[#This Row],[Recurso]],Tabela2[],2,FALSE)</f>
-        <v>100</v>
-      </c>
-      <c r="M20" s="10">
-        <f>L20*J20</f>
+      <c r="V20" s="2">
         <v>2000</v>
-      </c>
-      <c r="T20" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="U20" s="6">
-        <v>16</v>
-      </c>
-      <c r="V20" s="2">
-        <v>1600</v>
       </c>
     </row>
     <row r="21" spans="8:22" x14ac:dyDescent="0.3">
       <c r="H21" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I21" s="9" t="s">
-        <v>14</v>
+        <v>26</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="J21" s="1">
         <v>32</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L21" s="10">
+        <v>19</v>
+      </c>
+      <c r="L21" s="9">
         <f>VLOOKUP(Tabela1[[#This Row],[Recurso]],Tabela2[],2,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="M21" s="10">
-        <f>L21*J21</f>
+      <c r="M21" s="9">
+        <f t="shared" si="0"/>
         <v>3200</v>
       </c>
       <c r="T21" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="U21" s="6">
-        <v>20</v>
+        <v>13</v>
+      </c>
+      <c r="U21" s="11">
+        <v>32</v>
       </c>
       <c r="V21" s="2">
-        <v>2000</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="22" spans="8:22" x14ac:dyDescent="0.3">
       <c r="H22" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>15</v>
+        <v>26</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>14</v>
       </c>
       <c r="J22" s="1">
         <v>20</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L22" s="10">
+        <v>19</v>
+      </c>
+      <c r="L22" s="9">
         <f>VLOOKUP(Tabela1[[#This Row],[Recurso]],Tabela2[],2,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="M22" s="10">
-        <f>L22*J22</f>
+      <c r="M22" s="9">
+        <f t="shared" si="0"/>
         <v>2000</v>
       </c>
       <c r="T22" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="U22" s="6">
-        <v>32</v>
+        <v>11</v>
+      </c>
+      <c r="U22" s="11">
+        <v>16</v>
       </c>
       <c r="V22" s="2">
-        <v>3200</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="23" spans="8:22" x14ac:dyDescent="0.3">
       <c r="H23" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="J23" s="1">
         <v>4</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="L23" s="10">
+        <v>23</v>
+      </c>
+      <c r="L23" s="9">
         <f>VLOOKUP(Tabela1[[#This Row],[Recurso]],Tabela2[],2,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="M23" s="10">
-        <f>L23*J23</f>
+      <c r="M23" s="9">
+        <f t="shared" si="0"/>
         <v>480</v>
       </c>
       <c r="T23" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="U23" s="6">
-        <v>16</v>
+        <v>7</v>
+      </c>
+      <c r="U23" s="11">
+        <v>20</v>
       </c>
       <c r="V23" s="2">
-        <v>1600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="24" spans="8:22" x14ac:dyDescent="0.3">
       <c r="H24" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I24" s="9"/>
+        <v>36</v>
+      </c>
+      <c r="I24" s="8"/>
       <c r="J24" s="1">
         <f>SUBTOTAL(109,Tabela1[Horas])</f>
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
-      <c r="M24" s="10">
+      <c r="M24" s="9">
         <f>SUBTOTAL(109,Tabela1[Valor Total])</f>
-        <v>37940</v>
+        <v>38940</v>
       </c>
       <c r="T24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="U24" s="6">
+        <v>3</v>
+      </c>
+      <c r="U24" s="11">
         <v>20</v>
       </c>
       <c r="V24" s="2">
@@ -1801,20 +1792,20 @@
     </row>
     <row r="25" spans="8:22" x14ac:dyDescent="0.3">
       <c r="T25" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="U25" s="6">
-        <v>20</v>
+        <v>39</v>
+      </c>
+      <c r="U25" s="11">
+        <v>40</v>
       </c>
       <c r="V25" s="2">
-        <v>2000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="26" spans="8:22" x14ac:dyDescent="0.3">
       <c r="T26" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="U26" s="6">
+      <c r="U26" s="11">
         <v>24</v>
       </c>
       <c r="V26" s="2">
@@ -1823,9 +1814,9 @@
     </row>
     <row r="27" spans="8:22" x14ac:dyDescent="0.3">
       <c r="T27" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="U27" s="6">
+        <v>27</v>
+      </c>
+      <c r="U27" s="11">
         <v>24</v>
       </c>
       <c r="V27" s="2">
@@ -1833,14 +1824,29 @@
       </c>
     </row>
     <row r="28" spans="8:22" x14ac:dyDescent="0.3">
+      <c r="M28">
+        <v>38940</v>
+      </c>
       <c r="T28" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="U28" s="6">
-        <v>388</v>
+        <v>33</v>
+      </c>
+      <c r="U28" s="11">
+        <v>398</v>
       </c>
       <c r="V28" s="2">
-        <v>37940</v>
+        <v>38940</v>
+      </c>
+    </row>
+    <row r="29" spans="8:22" x14ac:dyDescent="0.3">
+      <c r="M29">
+        <f>M28/3</f>
+        <v>12980</v>
+      </c>
+    </row>
+    <row r="31" spans="8:22" x14ac:dyDescent="0.3">
+      <c r="M31">
+        <f>M28-M29</f>
+        <v>25960</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Requisitos.xlsx
+++ b/Docs/Requisitos.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a0706bd09e6b5aa/Trabalho/DEV/GestaoPiscina/Docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{9E92D66D-165D-42BC-BCAC-25A90C099D40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAD9F22D-9A6A-4DF6-992B-A61449716292}"/>
+  <xr:revisionPtr revIDLastSave="111" documentId="8_{9E92D66D-165D-42BC-BCAC-25A90C099D40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EB6432F-7514-4E82-8B70-5765F2215FD9}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{0FF7F3A3-45CB-4B48-859E-5FE7B9E0D8E5}"/>
+    <workbookView xWindow="34005" yWindow="0" windowWidth="33195" windowHeight="15480" xr2:uid="{0FF7F3A3-45CB-4B48-859E-5FE7B9E0D8E5}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha2" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="43" r:id="rId2"/>
+    <pivotCache cacheId="0" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="51">
   <si>
     <t>Recurso</t>
   </si>
@@ -159,6 +159,39 @@
   </si>
   <si>
     <t>Cadastros básicos: Clientes, Piscinas, Produtos, Síndicos e Usuários</t>
+  </si>
+  <si>
+    <t>Fase 4</t>
+  </si>
+  <si>
+    <t>Condição de pagamento</t>
+  </si>
+  <si>
+    <t>Parcela 2</t>
+  </si>
+  <si>
+    <t>Parcela 1 - Na assinatura do contrato</t>
+  </si>
+  <si>
+    <t>Parcela 3</t>
+  </si>
+  <si>
+    <t>Parcela 6</t>
+  </si>
+  <si>
+    <t>Parcela 4</t>
+  </si>
+  <si>
+    <t>Parcela 5</t>
+  </si>
+  <si>
+    <t>Parcela 7</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>Vencimento</t>
   </si>
 </sst>
 </file>
@@ -168,7 +201,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -182,16 +215,28 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -199,11 +244,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -231,19 +300,65 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="19">
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -253,25 +368,17 @@
       <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -533,7 +640,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B852A398-2C91-44C4-B090-B55E20C8CCE9}" name="Tabela dinâmica2" cacheId="43" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Recurso &gt; Item">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B852A398-2C91-44C4-B090-B55E20C8CCE9}" name="Tabela dinâmica2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Recurso &gt; Item">
   <location ref="T2:V28" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField showAll="0"/>
@@ -689,17 +796,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C67377A9-8B67-4460-B9FA-2F431678656F}" name="Tabela1" displayName="Tabela1" ref="H2:M24" totalsRowCount="1" headerRowDxfId="14" dataDxfId="13" totalsRowDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C67377A9-8B67-4460-B9FA-2F431678656F}" name="Tabela1" displayName="Tabela1" ref="H2:M24" totalsRowCount="1" headerRowDxfId="18" dataDxfId="17" totalsRowDxfId="16">
   <autoFilter ref="H2:M23" xr:uid="{C67377A9-8B67-4460-B9FA-2F431678656F}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{9A00E71B-0C22-4676-B207-02FEAD7B1D46}" name="Fase" totalsRowLabel="Total" dataDxfId="11" totalsRowDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{5FB9431E-42B7-4383-821B-59A8167AFBFC}" name="Item" dataDxfId="9" totalsRowDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{C2B35993-B025-42F7-831A-366A5C1002A2}" name="Horas" totalsRowFunction="sum" dataDxfId="7" totalsRowDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{9C63D28F-2D75-4750-9E8C-F8C8EFA23D8F}" name="Recurso" dataDxfId="5" totalsRowDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{92E94915-15DE-4828-86C2-9DF73A0005EF}" name="Valor Unit." dataDxfId="3" totalsRowDxfId="2">
+    <tableColumn id="1" xr3:uid="{9A00E71B-0C22-4676-B207-02FEAD7B1D46}" name="Fase" totalsRowLabel="Total" dataDxfId="15" totalsRowDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{5FB9431E-42B7-4383-821B-59A8167AFBFC}" name="Item" dataDxfId="14" totalsRowDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{C2B35993-B025-42F7-831A-366A5C1002A2}" name="Horas" totalsRowFunction="sum" dataDxfId="13" totalsRowDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{9C63D28F-2D75-4750-9E8C-F8C8EFA23D8F}" name="Recurso" dataDxfId="12" totalsRowDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{92E94915-15DE-4828-86C2-9DF73A0005EF}" name="Valor Unit." dataDxfId="11" totalsRowDxfId="5">
       <calculatedColumnFormula>VLOOKUP(Tabela1[[#This Row],[Recurso]],Tabela2[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{E7D5748C-E54E-48F9-A92A-197C4B2B2159}" name="Valor Total" totalsRowFunction="sum" dataDxfId="1" totalsRowDxfId="0">
+    <tableColumn id="6" xr3:uid="{E7D5748C-E54E-48F9-A92A-197C4B2B2159}" name="Valor Total" totalsRowFunction="sum" dataDxfId="10" totalsRowDxfId="4">
       <calculatedColumnFormula>L3*J3</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -713,6 +820,21 @@
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{BE19F672-651E-4DC9-AD38-CB2F8C950FCC}" name="Recurso"/>
     <tableColumn id="2" xr3:uid="{29803E43-FB5B-49AA-A8BA-DF12305079A8}" name="Valor"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{AA1C7815-65CB-44A9-83A7-CD25047265E2}" name="Tabela3" displayName="Tabela3" ref="I34:L41" totalsRowShown="0">
+  <autoFilter ref="I34:L41" xr:uid="{AA1C7815-65CB-44A9-83A7-CD25047265E2}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{2BE9BC46-F8AC-413B-AEFA-92E1EEF17B23}" name="Condição de pagamento" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{28DA2568-6968-4476-8DA1-70A3DA9F035A}" name="%" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{6B7A7CE1-B63A-4E39-A4EB-592CE431FA72}" name="Valor" dataDxfId="1">
+      <calculatedColumnFormula>J35*$L$30</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{3522202C-A0F5-48FD-9806-398C40750B42}" name="Vencimento" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1035,16 +1157,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48E4F75F-1DD9-4A91-8E30-81F4CE3B2615}">
-  <dimension ref="B2:V31"/>
+  <dimension ref="B2:V43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="46.109375" style="6" customWidth="1"/>
+    <col min="9" max="9" width="40.77734375" style="6" customWidth="1"/>
     <col min="10" max="10" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.5546875" customWidth="1"/>
-    <col min="12" max="12" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="13.44140625" customWidth="1"/>
+    <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="74" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.109375" bestFit="1" customWidth="1"/>
@@ -1116,7 +1238,7 @@
       <c r="T3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="U3" s="11">
+      <c r="U3">
         <v>32</v>
       </c>
       <c r="V3" s="2">
@@ -1153,7 +1275,7 @@
       <c r="T4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="U4" s="11">
+      <c r="U4">
         <v>20</v>
       </c>
       <c r="V4" s="2">
@@ -1190,7 +1312,7 @@
       <c r="T5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="U5" s="11">
+      <c r="U5">
         <v>8</v>
       </c>
       <c r="V5" s="2">
@@ -1227,7 +1349,7 @@
       <c r="T6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="U6" s="11">
+      <c r="U6">
         <v>4</v>
       </c>
       <c r="V6" s="2">
@@ -1239,10 +1361,10 @@
         <v>24</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J7" s="1">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>19</v>
@@ -1252,28 +1374,28 @@
         <v>100</v>
       </c>
       <c r="M7" s="9">
-        <f t="shared" si="0"/>
-        <v>2000</v>
+        <f>L7*J7</f>
+        <v>800</v>
       </c>
       <c r="T7" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="U7" s="11">
+      <c r="U7">
         <v>36</v>
       </c>
       <c r="V7" s="2">
         <v>2700</v>
       </c>
     </row>
-    <row r="8" spans="2:22" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.3">
       <c r="H8" s="1" t="s">
         <v>24</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J8" s="1">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>19</v>
@@ -1283,13 +1405,13 @@
         <v>100</v>
       </c>
       <c r="M8" s="9">
-        <f t="shared" si="0"/>
-        <v>2000</v>
+        <f>L8*J8</f>
+        <v>1600</v>
       </c>
       <c r="T8" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="U8" s="11">
+      <c r="U8">
         <v>4</v>
       </c>
       <c r="V8" s="2">
@@ -1300,27 +1422,27 @@
       <c r="H9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I9" s="7" t="s">
-        <v>5</v>
+      <c r="I9" s="8" t="s">
+        <v>27</v>
       </c>
       <c r="J9" s="1">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="L9" s="9">
         <f>VLOOKUP(Tabela1[[#This Row],[Recurso]],Tabela2[],2,FALSE)</f>
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="M9" s="9">
-        <f t="shared" si="0"/>
-        <v>800</v>
+        <f>L9*J9</f>
+        <v>1800</v>
       </c>
       <c r="T9" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="U9" s="11">
+      <c r="U9">
         <v>16</v>
       </c>
       <c r="V9" s="2">
@@ -1332,26 +1454,26 @@
         <v>24</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="J10" s="1">
         <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L10" s="9">
         <f>VLOOKUP(Tabela1[[#This Row],[Recurso]],Tabela2[],2,FALSE)</f>
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="M10" s="9">
-        <f t="shared" si="0"/>
-        <v>1600</v>
+        <f>L10*J10</f>
+        <v>1200</v>
       </c>
       <c r="T10" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="U10" s="11">
+      <c r="U10">
         <v>16</v>
       </c>
       <c r="V10" s="2">
@@ -1362,27 +1484,27 @@
       <c r="H11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I11" s="8" t="s">
-        <v>27</v>
+      <c r="I11" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="J11" s="1">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="L11" s="9">
         <f>VLOOKUP(Tabela1[[#This Row],[Recurso]],Tabela2[],2,FALSE)</f>
         <v>75</v>
       </c>
       <c r="M11" s="9">
-        <f t="shared" si="0"/>
-        <v>1800</v>
+        <f>L11*J11</f>
+        <v>300</v>
       </c>
       <c r="T11" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U11" s="11">
+      <c r="U11">
         <v>306</v>
       </c>
       <c r="V11" s="2">
@@ -1394,7 +1516,7 @@
         <v>24</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J12" s="1">
         <v>16</v>
@@ -1407,13 +1529,13 @@
         <v>75</v>
       </c>
       <c r="M12" s="9">
-        <f t="shared" si="0"/>
+        <f>L12*J12</f>
         <v>1200</v>
       </c>
       <c r="T12" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="U12" s="11">
+      <c r="U12">
         <v>8</v>
       </c>
       <c r="V12" s="2">
@@ -1422,60 +1544,60 @@
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.3">
       <c r="H13" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="J13" s="1">
-        <v>4</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L13" s="9">
+        <v>25</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="J13" s="12">
+        <v>20</v>
+      </c>
+      <c r="K13" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="L13" s="13">
         <f>VLOOKUP(Tabela1[[#This Row],[Recurso]],Tabela2[],2,FALSE)</f>
-        <v>75</v>
-      </c>
-      <c r="M13" s="9">
-        <f t="shared" si="0"/>
-        <v>300</v>
+        <v>100</v>
+      </c>
+      <c r="M13" s="14">
+        <f>L13*J13</f>
+        <v>2000</v>
       </c>
       <c r="T13" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="U13" s="11">
+      <c r="U13">
         <v>20</v>
       </c>
       <c r="V13" s="2">
         <v>2000</v>
       </c>
     </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="H14" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J14" s="1">
-        <v>16</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L14" s="9">
+        <v>25</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="16">
+        <v>20</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="L14" s="17">
         <f>VLOOKUP(Tabela1[[#This Row],[Recurso]],Tabela2[],2,FALSE)</f>
-        <v>75</v>
-      </c>
-      <c r="M14" s="9">
-        <f t="shared" si="0"/>
-        <v>1200</v>
+        <v>100</v>
+      </c>
+      <c r="M14" s="18">
+        <f>L14*J14</f>
+        <v>2000</v>
       </c>
       <c r="T14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="11">
+      <c r="U14">
         <v>20</v>
       </c>
       <c r="V14" s="2">
@@ -1484,7 +1606,7 @@
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.3">
       <c r="H15" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I15" s="8" t="s">
         <v>7</v>
@@ -1500,13 +1622,13 @@
         <v>100</v>
       </c>
       <c r="M15" s="9">
-        <f t="shared" si="0"/>
+        <f>L15*J15</f>
         <v>2000</v>
       </c>
       <c r="T15" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="U15" s="11">
+      <c r="U15">
         <v>20</v>
       </c>
       <c r="V15" s="2">
@@ -1515,7 +1637,7 @@
     </row>
     <row r="16" spans="2:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="H16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>8</v>
@@ -1531,13 +1653,13 @@
         <v>100</v>
       </c>
       <c r="M16" s="9">
-        <f t="shared" si="0"/>
+        <f>L16*J16</f>
         <v>2000</v>
       </c>
       <c r="T16" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="U16" s="11">
+      <c r="U16">
         <v>20</v>
       </c>
       <c r="V16" s="2">
@@ -1546,7 +1668,7 @@
     </row>
     <row r="17" spans="8:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="H17" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I17" s="8" t="s">
         <v>9</v>
@@ -1562,13 +1684,13 @@
         <v>100</v>
       </c>
       <c r="M17" s="9">
-        <f t="shared" si="0"/>
+        <f>L17*J17</f>
         <v>2400</v>
       </c>
       <c r="T17" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="U17" s="11">
+      <c r="U17">
         <v>30</v>
       </c>
       <c r="V17" s="2">
@@ -1577,7 +1699,7 @@
     </row>
     <row r="18" spans="8:22" x14ac:dyDescent="0.3">
       <c r="H18" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I18" s="8" t="s">
         <v>10</v>
@@ -1593,13 +1715,13 @@
         <v>100</v>
       </c>
       <c r="M18" s="9">
-        <f t="shared" si="0"/>
+        <f>L18*J18</f>
         <v>2000</v>
       </c>
       <c r="T18" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="U18" s="11">
+      <c r="U18">
         <v>24</v>
       </c>
       <c r="V18" s="2">
@@ -1608,7 +1730,7 @@
     </row>
     <row r="19" spans="8:22" x14ac:dyDescent="0.3">
       <c r="H19" s="1" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I19" s="8" t="s">
         <v>11</v>
@@ -1624,7 +1746,7 @@
         <v>100</v>
       </c>
       <c r="M19" s="9">
-        <f t="shared" si="0"/>
+        <f>L19*J19</f>
         <v>1600</v>
       </c>
       <c r="P19" s="2">
@@ -1634,7 +1756,7 @@
       <c r="T19" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="U19" s="11">
+      <c r="U19">
         <v>16</v>
       </c>
       <c r="V19" s="2">
@@ -1643,7 +1765,7 @@
     </row>
     <row r="20" spans="8:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="H20" s="1" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I20" s="8" t="s">
         <v>12</v>
@@ -1659,13 +1781,13 @@
         <v>100</v>
       </c>
       <c r="M20" s="9">
-        <f t="shared" si="0"/>
+        <f>L20*J20</f>
         <v>2000</v>
       </c>
       <c r="T20" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="U20" s="11">
+      <c r="U20">
         <v>20</v>
       </c>
       <c r="V20" s="2">
@@ -1674,7 +1796,7 @@
     </row>
     <row r="21" spans="8:22" x14ac:dyDescent="0.3">
       <c r="H21" s="1" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I21" s="8" t="s">
         <v>13</v>
@@ -1690,13 +1812,13 @@
         <v>100</v>
       </c>
       <c r="M21" s="9">
-        <f t="shared" si="0"/>
+        <f>L21*J21</f>
         <v>3200</v>
       </c>
       <c r="T21" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="U21" s="11">
+      <c r="U21">
         <v>32</v>
       </c>
       <c r="V21" s="2">
@@ -1705,7 +1827,7 @@
     </row>
     <row r="22" spans="8:22" x14ac:dyDescent="0.3">
       <c r="H22" s="1" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I22" s="8" t="s">
         <v>14</v>
@@ -1721,13 +1843,13 @@
         <v>100</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" si="0"/>
+        <f>L22*J22</f>
         <v>2000</v>
       </c>
       <c r="T22" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="U22" s="11">
+      <c r="U22">
         <v>16</v>
       </c>
       <c r="V22" s="2">
@@ -1736,7 +1858,7 @@
     </row>
     <row r="23" spans="8:22" x14ac:dyDescent="0.3">
       <c r="H23" s="1" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I23" s="8" t="s">
         <v>22</v>
@@ -1752,13 +1874,13 @@
         <v>120</v>
       </c>
       <c r="M23" s="9">
-        <f t="shared" si="0"/>
+        <f>L23*J23</f>
         <v>480</v>
       </c>
       <c r="T23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="U23" s="11">
+      <c r="U23">
         <v>20</v>
       </c>
       <c r="V23" s="2">
@@ -1783,7 +1905,7 @@
       <c r="T24" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="U24" s="11">
+      <c r="U24">
         <v>20</v>
       </c>
       <c r="V24" s="2">
@@ -1794,7 +1916,7 @@
       <c r="T25" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="U25" s="11">
+      <c r="U25">
         <v>40</v>
       </c>
       <c r="V25" s="2">
@@ -1805,7 +1927,7 @@
       <c r="T26" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="U26" s="11">
+      <c r="U26">
         <v>24</v>
       </c>
       <c r="V26" s="2">
@@ -1816,7 +1938,7 @@
       <c r="T27" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="U27" s="11">
+      <c r="U27">
         <v>24</v>
       </c>
       <c r="V27" s="2">
@@ -1824,13 +1946,14 @@
       </c>
     </row>
     <row r="28" spans="8:22" x14ac:dyDescent="0.3">
-      <c r="M28">
+      <c r="L28" s="2">
+        <f>Tabela1[[#Totals],[Valor Total]]</f>
         <v>38940</v>
       </c>
       <c r="T28" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="U28" s="11">
+      <c r="U28">
         <v>398</v>
       </c>
       <c r="V28" s="2">
@@ -1838,23 +1961,169 @@
       </c>
     </row>
     <row r="29" spans="8:22" x14ac:dyDescent="0.3">
-      <c r="M29">
-        <f>M28/3</f>
-        <v>12980</v>
-      </c>
-    </row>
-    <row r="31" spans="8:22" x14ac:dyDescent="0.3">
-      <c r="M31">
-        <f>M28-M29</f>
-        <v>25960</v>
+      <c r="J29" s="19">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="K29" s="2">
+        <f>L28*J29</f>
+        <v>12967.02</v>
+      </c>
+      <c r="L29" s="2">
+        <f>ROUND(K29,0)</f>
+        <v>12967</v>
+      </c>
+    </row>
+    <row r="30" spans="8:22" x14ac:dyDescent="0.3">
+      <c r="K30" s="2">
+        <f>L28-K29</f>
+        <v>25972.98</v>
+      </c>
+      <c r="L30" s="2">
+        <f>ROUND(K30,0)</f>
+        <v>25973</v>
+      </c>
+    </row>
+    <row r="34" spans="9:12" x14ac:dyDescent="0.3">
+      <c r="I34" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K34" t="s">
+        <v>38</v>
+      </c>
+      <c r="L34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="9:12" x14ac:dyDescent="0.3">
+      <c r="I35" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J35" s="20">
+        <v>0.2</v>
+      </c>
+      <c r="K35" s="2">
+        <f>J35*$L$30</f>
+        <v>5194.6000000000004</v>
+      </c>
+      <c r="L35" s="21">
+        <v>45874</v>
+      </c>
+    </row>
+    <row r="36" spans="9:12" x14ac:dyDescent="0.3">
+      <c r="I36" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J36" s="20">
+        <v>0.1</v>
+      </c>
+      <c r="K36" s="2">
+        <f t="shared" ref="K36:K38" si="1">J36*$L$30</f>
+        <v>2597.3000000000002</v>
+      </c>
+      <c r="L36" s="21">
+        <v>45905</v>
+      </c>
+    </row>
+    <row r="37" spans="9:12" x14ac:dyDescent="0.3">
+      <c r="I37" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J37" s="20">
+        <v>0.1</v>
+      </c>
+      <c r="K37" s="2">
+        <f t="shared" si="1"/>
+        <v>2597.3000000000002</v>
+      </c>
+      <c r="L37" s="21">
+        <v>45935</v>
+      </c>
+    </row>
+    <row r="38" spans="9:12" x14ac:dyDescent="0.3">
+      <c r="I38" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="J38" s="20">
+        <v>0.1</v>
+      </c>
+      <c r="K38" s="2">
+        <f t="shared" si="1"/>
+        <v>2597.3000000000002</v>
+      </c>
+      <c r="L38" s="21">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="39" spans="9:12" x14ac:dyDescent="0.3">
+      <c r="I39" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J39" s="20">
+        <v>0.1</v>
+      </c>
+      <c r="K39" s="2">
+        <f t="shared" ref="K39:K42" si="2">J39*$L$30</f>
+        <v>2597.3000000000002</v>
+      </c>
+      <c r="L39" s="21">
+        <v>45996</v>
+      </c>
+    </row>
+    <row r="40" spans="9:12" x14ac:dyDescent="0.3">
+      <c r="I40" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J40" s="20">
+        <v>0.2</v>
+      </c>
+      <c r="K40" s="2">
+        <f t="shared" si="2"/>
+        <v>5194.6000000000004</v>
+      </c>
+      <c r="L40" s="21">
+        <v>46027</v>
+      </c>
+    </row>
+    <row r="41" spans="9:12" x14ac:dyDescent="0.3">
+      <c r="I41" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="J41" s="20">
+        <v>0.2</v>
+      </c>
+      <c r="K41" s="2">
+        <f t="shared" si="2"/>
+        <v>5194.6000000000004</v>
+      </c>
+      <c r="L41" s="21">
+        <v>46058</v>
+      </c>
+    </row>
+    <row r="42" spans="9:12" x14ac:dyDescent="0.3">
+      <c r="J42" s="20"/>
+      <c r="K42" s="2"/>
+    </row>
+    <row r="43" spans="9:12" x14ac:dyDescent="0.3">
+      <c r="J43" s="20">
+        <f>SUM(J35:J42)</f>
+        <v>1</v>
+      </c>
+      <c r="K43" s="2">
+        <f>SUM(K35:K42)</f>
+        <v>25973</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
-  <tableParts count="2">
+  <tableParts count="3">
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>